--- a/data/trans_dic/IQ2601_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ2601_R2-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45,01%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>58,73%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65,29%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>60,47%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>61,64%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,73%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,33; 71,71</t>
+          <t>48,87; 69,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,25; 52,0</t>
+          <t>35,22; 55,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,28; 71,56</t>
+          <t>48,27; 68,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,17; 90,61</t>
+          <t>44,28; 82,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,37; 70,67</t>
+          <t>49,87; 70,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,71; 55,01</t>
+          <t>32,04; 53,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,47; 68,35</t>
+          <t>51,35; 72,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,04; 84,09</t>
+          <t>51,25; 90,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 67,55</t>
+          <t>51,7; 67,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,14; 51,47</t>
+          <t>36,26; 51,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,56; 67,56</t>
+          <t>53,05; 67,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,98; 82,29</t>
+          <t>52,34; 81,33</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>44,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63,59%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>88,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>50,64%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>62,14%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>72,39%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,03; 93,37</t>
+          <t>89,95; 97,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,01; 59,21</t>
+          <t>36,46; 52,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,99; 69,46</t>
+          <t>54,28; 69,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,81; 87,11</t>
+          <t>45,27; 81,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,16; 97,48</t>
+          <t>83,49; 93,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,29; 52,38</t>
+          <t>42,7; 58,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,21; 69,59</t>
+          <t>54,0; 69,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,26; 81,37</t>
+          <t>50,35; 84,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,02; 94,46</t>
+          <t>88,13; 94,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41,22; 52,69</t>
+          <t>42,44; 53,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,69; 67,59</t>
+          <t>56,88; 67,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,51; 79,86</t>
+          <t>51,39; 77,49</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>35,96%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69,56%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>49,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>41,6%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>66,08%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61,62%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,56%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,57; 58,85</t>
+          <t>27,17; 45,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,41; 52,65</t>
+          <t>25,47; 44,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,91; 75,71</t>
+          <t>59,96; 78,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,78; 78,15</t>
+          <t>41,06; 78,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,07; 44,96</t>
+          <t>39,12; 58,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,15; 43,45</t>
+          <t>31,98; 51,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,56; 78,29</t>
+          <t>54,04; 76,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41,4; 78,53</t>
+          <t>40,88; 76,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,75; 49,53</t>
+          <t>35,59; 49,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,36; 45,45</t>
+          <t>31,01; 45,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,45; 74,93</t>
+          <t>60,47; 74,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,48; 74,25</t>
+          <t>46,0; 72,55</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>70,21%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>68,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>62,93%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>58,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,17; 78,04</t>
+          <t>49,15; 67,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,36; 76,77</t>
+          <t>51,94; 70,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,63; 71,05</t>
+          <t>58,82; 75,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 84,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,38; 66,39</t>
+          <t>61,48; 78,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,01; 70,17</t>
+          <t>58,86; 77,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,26; 76,28</t>
+          <t>52,59; 71,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,22; 84,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,85; 70,05</t>
+          <t>57,8; 70,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,43; 71,59</t>
+          <t>59,08; 72,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,78; 71,84</t>
+          <t>58,92; 72,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,43; 91,2</t>
+          <t>54,74; 91,29</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>59,32%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61,37%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75,66%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>71,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>64,25%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>88,17%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>74,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>75,66%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,82; 82,31</t>
+          <t>45,3; 71,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,9; 75,34</t>
+          <t>48,81; 72,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,14; 95,71</t>
+          <t>64,1; 85,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52,9; 91,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,06; 70,56</t>
+          <t>59,54; 81,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,62; 71,91</t>
+          <t>52,05; 77,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,64; 84,95</t>
+          <t>77,49; 94,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,69; 89,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,5; 73,54</t>
+          <t>56,62; 73,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53,29; 70,78</t>
+          <t>53,53; 70,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,0; 87,63</t>
+          <t>73,77; 87,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,93; 96,0</t>
+          <t>75,17; 94,65</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>47,84%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>41,47%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>40,09%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>47,93%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>58,06%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,04; 52,92</t>
+          <t>38,61; 58,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,99; 52,7</t>
+          <t>23,71; 44,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,28; 59,13</t>
+          <t>40,97; 62,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,08; 82,75</t>
+          <t>38,45; 78,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,85; 58,62</t>
+          <t>31,21; 52,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,26; 45,59</t>
+          <t>29,43; 52,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,94; 62,51</t>
+          <t>36,23; 58,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,44; 76,05</t>
+          <t>30,41; 78,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,64; 52,38</t>
+          <t>37,54; 52,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,21; 44,81</t>
+          <t>29,81; 45,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42,06; 57,76</t>
+          <t>41,85; 57,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,58; 72,56</t>
+          <t>41,19; 71,77</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60,87%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45,24%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>64,54%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69,53%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>60,38%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>46,94%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>63,2%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>69,36%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>60,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,54%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,92; 67,24</t>
+          <t>53,96; 67,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,97; 54,45</t>
+          <t>37,92; 52,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,93; 69,5</t>
+          <t>57,92; 70,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54,69; 83,51</t>
+          <t>57,13; 81,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,73; 67,17</t>
+          <t>52,99; 67,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,51; 53,14</t>
+          <t>39,71; 53,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,91; 70,67</t>
+          <t>56,66; 69,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,03; 81,94</t>
+          <t>48,01; 79,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,67; 65,57</t>
+          <t>55,57; 65,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41,12; 51,14</t>
+          <t>41,4; 51,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,14; 68,26</t>
+          <t>59,06; 68,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,68; 78,83</t>
+          <t>56,27; 77,13</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>65,19%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>78,49%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>59,49%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>65,54%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>58,19%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>65,19%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>72,78; 83,54</t>
+          <t>70,42; 80,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>53,32; 65,43</t>
+          <t>51,57; 64,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,9; 71,36</t>
+          <t>59,41; 71,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60,06; 87,81</t>
+          <t>69,78; 92,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,18; 81,03</t>
+          <t>73,15; 83,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,19; 63,93</t>
+          <t>53,8; 65,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,86; 70,73</t>
+          <t>59,15; 71,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>71,17; 93,08</t>
+          <t>61,07; 89,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73,18; 80,76</t>
+          <t>73,21; 80,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,47; 63,29</t>
+          <t>54,33; 63,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61,19; 69,42</t>
+          <t>61,22; 69,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,73; 88,25</t>
+          <t>71,53; 88,63</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65,02; 70,61</t>
+          <t>62,22; 68,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49,05; 55,47</t>
+          <t>45,83; 52,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61,16; 66,79</t>
+          <t>61,19; 67,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62,91; 75,68</t>
+          <t>67,04; 78,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62,17; 67,92</t>
+          <t>65,16; 70,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,69; 52,07</t>
+          <t>49,44; 55,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,56; 67,25</t>
+          <t>60,93; 66,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67,0; 79,36</t>
+          <t>61,36; 74,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64,67; 68,55</t>
+          <t>64,54; 68,67</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48,65; 53,02</t>
+          <t>48,66; 53,14</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61,99; 66,26</t>
+          <t>62,25; 66,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67,07; 75,65</t>
+          <t>66,6; 75,37</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27932</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37855</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11470</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>29862</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23579</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10195</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33115</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27932</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37855</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>20656</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24360; 35415</t>
+          <t>27054; 38745</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17388; 28937</t>
+          <t>21855; 34544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29181; 40722</t>
+          <t>31115; 44197</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7291; 12197</t>
+          <t>7778; 14429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27333; 39124</t>
+          <t>24627; 35057</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20915; 34136</t>
+          <t>17830; 29924</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31244; 44057</t>
+          <t>29219; 40985</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9274; 17314</t>
+          <t>6337; 11132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54746; 70756</t>
+          <t>54150; 70425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42543; 60579</t>
+          <t>42683; 60974</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63793; 81997</t>
+          <t>64383; 81498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18041; 28019</t>
+          <t>15665; 24344</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101561</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46313</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67662</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18387</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>86535</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>50979</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>63511</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16322</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>101561</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46313</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67662</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>31981</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80743; 90802</t>
+          <t>96662; 104717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43300; 59611</t>
+          <t>38176; 55093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55184; 70988</t>
+          <t>59162; 75319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12134; 19642</t>
+          <t>13090; 23467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96883; 104756</t>
+          <t>81191; 90965</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37991; 54836</t>
+          <t>42989; 59074</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59085; 75858</t>
+          <t>55184; 71117</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14708; 26444</t>
+          <t>10010; 16778</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180187; 193374</t>
+          <t>180397; 193419</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84658; 108219</t>
+          <t>87165; 109500</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119732; 142760</t>
+          <t>120134; 142753</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30008; 43962</t>
+          <t>25078; 37811</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24831</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23454</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47698</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>32594</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>27211</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>41371</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11468</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>24831</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23454</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47698</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>20003</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25497; 38906</t>
+          <t>18763; 31156</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20546; 34442</t>
+          <t>17444; 30692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34379; 47401</t>
+          <t>41115; 53590</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8148; 14545</t>
+          <t>5806; 11068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18694; 31048</t>
+          <t>25858; 38911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16541; 29751</t>
+          <t>20920; 33551</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41527; 53686</t>
+          <t>33832; 47688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6652; 12616</t>
+          <t>7650; 14400</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48316; 66938</t>
+          <t>48106; 66986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41985; 60852</t>
+          <t>41524; 60387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79300; 98294</t>
+          <t>79332; 97174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17160; 25746</t>
+          <t>15112; 23836</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45827</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>50956</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54925</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10578</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>51237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>51369</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>47759</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9216</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>45827</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50956</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54925</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>20235</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44638; 56951</t>
+          <t>38588; 52663</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44265; 57254</t>
+          <t>42715; 58277</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39943; 53917</t>
+          <t>47753; 61572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5249; 12328</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37986; 52125</t>
+          <t>44865; 57137</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42769; 57704</t>
+          <t>43894; 57477</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47294; 61927</t>
+          <t>39911; 54259</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5665; 12877</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87639; 106123</t>
+          <t>87555; 106613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91617; 112255</t>
+          <t>92642; 113020</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92328; 112836</t>
+          <t>92548; 113204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14643; 23254</t>
+          <t>14121; 23549</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>26203</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28277</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34493</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11044</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>29125</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28207</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>37775</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7655</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26203</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28277</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34493</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>19019</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24254; 33371</t>
+          <t>20008; 31592</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22347; 33074</t>
+          <t>22492; 33535</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33474; 41004</t>
+          <t>29221; 38997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5439; 9401</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21229; 31166</t>
+          <t>24138; 33116</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21942; 33133</t>
+          <t>22849; 33836</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29012; 38726</t>
+          <t>33196; 40555</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5729; 9546</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47863; 62300</t>
+          <t>47962; 62338</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47952; 63687</t>
+          <t>48161; 63828</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64555; 77488</t>
+          <t>65234; 77466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15883; 20081</t>
+          <t>16322; 20551</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>28280</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19123</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30050</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9168</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>23246</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>21137</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>25700</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5155</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28280</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19123</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30050</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>14237</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17958; 29666</t>
+          <t>22821; 34298</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15812; 27786</t>
+          <t>13428; 25422</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19994; 31709</t>
+          <t>23653; 36371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2759; 7347</t>
+          <t>6096; 12391</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22372; 34650</t>
+          <t>17497; 29499</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13739; 25824</t>
+          <t>15516; 27669</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23637; 36092</t>
+          <t>19427; 31480</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7067; 13981</t>
+          <t>2706; 6976</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43347; 60321</t>
+          <t>43229; 59989</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31948; 49009</t>
+          <t>32599; 49924</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46840; 64318</t>
+          <t>46607; 64028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12153; 19782</t>
+          <t>10196; 17765</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>80697</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>62382</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>92182</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>28364</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>77262</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>62725</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>86450</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>19588</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>80697</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>62382</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>92182</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>45988</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>67716; 86043</t>
+          <t>71526; 89656</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53415; 72768</t>
+          <t>52292; 71946</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77862; 95054</t>
+          <t>82737; 101025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15445; 23583</t>
+          <t>23308; 33305</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>71225; 89037</t>
+          <t>67810; 86111</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53105; 73279</t>
+          <t>53069; 72096</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82713; 100947</t>
+          <t>77493; 95708</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24032; 35780</t>
+          <t>12960; 21553</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>145022; 170816</t>
+          <t>144781; 170756</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111652; 138857</t>
+          <t>112425; 139749</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>165372; 190873</t>
+          <t>165143; 191194</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>41478; 56684</t>
+          <t>38146; 52287</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>121960</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>97778</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>109482</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>33267</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>121175</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>95901</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>106627</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>19385</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>121960</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97778</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>109482</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>19798</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52323</t>
+          <t>53065</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>112360; 128970</t>
+          <t>113407; 129611</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>85953; 105478</t>
+          <t>86645; 107633</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97453; 116102</t>
+          <t>99779; 119649</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15242; 22282</t>
+          <t>27543; 36682</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>113021; 130487</t>
+          <t>112933; 128937</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>87690; 107415</t>
+          <t>86720; 105906</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98861; 118783</t>
+          <t>96234; 115526</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27820; 36381</t>
+          <t>15765; 23022</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>230838; 254738</t>
+          <t>230920; 253494</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>179323; 208369</t>
+          <t>178878; 208533</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>202308; 229544</t>
+          <t>202408; 229253</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45597; 56888</t>
+          <t>46698; 57862</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>462474</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>462474</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>432164; 469291</t>
+          <t>440089; 481463</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>337344; 381526</t>
+          <t>332768; 378199</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>424179; 463217</t>
+          <t>451187; 497019</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89370; 107503</t>
+          <t>119578; 140854</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>439742; 480392</t>
+          <t>433101; 470992</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>331716; 378087</t>
+          <t>340065; 382882</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>453926; 495865</t>
+          <t>422565; 463696</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>128483; 152196</t>
+          <t>85022; 103047</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>887289; 940472</t>
+          <t>885396; 942134</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>687891; 749600</t>
+          <t>687930; 751363</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>887063; 948036</t>
+          <t>890646; 946107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>223897; 252531</t>
+          <t>211054; 238878</t>
         </is>
       </c>
     </row>
